--- a/Function 2/evals.xlsx
+++ b/Function 2/evals.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prithvi\Desktop\Imperial Course\Capstone-Project\Function 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E565BE6-A158-4DD1-B939-F3FD9898A539}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ADAADDE-2447-429B-BB79-4A02FA277047}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -84,10 +84,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -377,38 +377,38 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3" t="s">
+      <c r="C2" s="4"/>
+      <c r="D2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3" t="s">
+      <c r="E2" s="4"/>
+      <c r="F2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3" t="s">
+      <c r="G2" s="4"/>
+      <c r="H2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="3"/>
+      <c r="I2" s="4"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B3" s="4">
+      <c r="B3" s="3">
         <v>1</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4">
+      <c r="C3" s="3"/>
+      <c r="D3" s="3">
         <v>0.71402200000000005</v>
       </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4">
+      <c r="E3" s="3"/>
+      <c r="F3" s="3">
         <v>0.14477200000000001</v>
       </c>
-      <c r="G3" s="4"/>
+      <c r="G3" s="3"/>
       <c r="H3" s="5">
         <v>0.59747244630609897</v>
       </c>
@@ -417,160 +417,168 @@
       <c r="K3" s="1"/>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B4" s="4">
+      <c r="B4" s="3">
         <v>2</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4">
+      <c r="C4" s="3"/>
+      <c r="D4" s="3">
         <v>0.74275198707938395</v>
       </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4">
+      <c r="E4" s="3"/>
+      <c r="F4" s="3">
         <v>0.88397478133732699</v>
       </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3">
+        <v>0.37689874596557199</v>
+      </c>
+      <c r="I4" s="3"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
+      <c r="B5" s="3">
+        <v>3</v>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3">
+        <v>0.67103219867563402</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3">
+        <v>1</v>
+      </c>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
     </row>
     <row r="14" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
@@ -578,42 +586,6 @@
     </row>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="D2:E2"/>
@@ -630,6 +602,42 @@
     <mergeCell ref="H10:I10"/>
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="F7:G7"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F12:G12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Function 2/evals.xlsx
+++ b/Function 2/evals.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prithvi\Desktop\Imperial Course\Capstone-Project\Function 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ADAADDE-2447-429B-BB79-4A02FA277047}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4149C02-99BA-4352-BFBE-77CF691E75DC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -84,10 +84,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -377,38 +377,38 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4" t="s">
+      <c r="C2" s="3"/>
+      <c r="D2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4" t="s">
+      <c r="E2" s="3"/>
+      <c r="F2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4" t="s">
+      <c r="G2" s="3"/>
+      <c r="H2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="4"/>
+      <c r="I2" s="3"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B3" s="3">
+      <c r="B3" s="4">
         <v>1</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3">
+      <c r="C3" s="4"/>
+      <c r="D3" s="4">
         <v>0.71402200000000005</v>
       </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3">
+      <c r="E3" s="4"/>
+      <c r="F3" s="4">
         <v>0.14477200000000001</v>
       </c>
-      <c r="G3" s="3"/>
+      <c r="G3" s="4"/>
       <c r="H3" s="5">
         <v>0.59747244630609897</v>
       </c>
@@ -417,168 +417,176 @@
       <c r="K3" s="1"/>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B4" s="3">
+      <c r="B4" s="4">
         <v>2</v>
       </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3">
+      <c r="C4" s="4"/>
+      <c r="D4" s="4">
         <v>0.74275198707938395</v>
       </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3">
+      <c r="E4" s="4"/>
+      <c r="F4" s="4">
         <v>0.88397478133732699</v>
       </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3">
+      <c r="G4" s="4"/>
+      <c r="H4" s="4">
         <v>0.37689874596557199</v>
       </c>
-      <c r="I4" s="3"/>
+      <c r="I4" s="4"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B5" s="3">
+      <c r="B5" s="4">
         <v>3</v>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3">
+      <c r="C5" s="4"/>
+      <c r="D5" s="4">
         <v>0.67103219867563402</v>
       </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3">
+      <c r="E5" s="4"/>
+      <c r="F5" s="4">
         <v>1</v>
       </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4">
+        <v>0.42858172097026598</v>
+      </c>
+      <c r="I5" s="4"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
+      <c r="B6" s="4">
+        <v>4</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4">
+        <v>0.69365732956012705</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4">
+        <v>0.387796793163461</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
     </row>
     <row r="14" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
@@ -586,6 +594,42 @@
     </row>
   </sheetData>
   <mergeCells count="52">
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="D2:E2"/>
@@ -602,42 +646,6 @@
     <mergeCell ref="H10:I10"/>
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="F7:G7"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F12:G12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Function 2/evals.xlsx
+++ b/Function 2/evals.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prithvi\Desktop\Imperial Course\Capstone-Project\Function 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4149C02-99BA-4352-BFBE-77CF691E75DC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C30A23B-3490-468F-8CED-5FCA8D87D394}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -84,10 +84,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -377,22 +377,22 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3" t="s">
+      <c r="C2" s="4"/>
+      <c r="D2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3" t="s">
+      <c r="E2" s="4"/>
+      <c r="F2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3" t="s">
+      <c r="G2" s="4"/>
+      <c r="H2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="3"/>
+      <c r="I2" s="4"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
     </row>
@@ -401,14 +401,14 @@
         <v>1</v>
       </c>
       <c r="C3" s="4"/>
-      <c r="D3" s="4">
+      <c r="D3" s="3">
         <v>0.71402200000000005</v>
       </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4">
+      <c r="E3" s="3"/>
+      <c r="F3" s="3">
         <v>0.14477200000000001</v>
       </c>
-      <c r="G3" s="4"/>
+      <c r="G3" s="3"/>
       <c r="H3" s="5">
         <v>0.59747244630609897</v>
       </c>
@@ -421,18 +421,18 @@
         <v>2</v>
       </c>
       <c r="C4" s="4"/>
-      <c r="D4" s="4">
+      <c r="D4" s="3">
         <v>0.74275198707938395</v>
       </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4">
+      <c r="E4" s="3"/>
+      <c r="F4" s="3">
         <v>0.88397478133732699</v>
       </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4">
+      <c r="G4" s="3"/>
+      <c r="H4" s="3">
         <v>0.37689874596557199</v>
       </c>
-      <c r="I4" s="4"/>
+      <c r="I4" s="3"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
@@ -443,18 +443,18 @@
         <v>3</v>
       </c>
       <c r="C5" s="4"/>
-      <c r="D5" s="4">
+      <c r="D5" s="3">
         <v>0.67103219867563402</v>
       </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4">
+      <c r="E5" s="3"/>
+      <c r="F5" s="3">
         <v>1</v>
       </c>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4">
+      <c r="G5" s="3"/>
+      <c r="H5" s="3">
         <v>0.42858172097026598</v>
       </c>
-      <c r="I5" s="4"/>
+      <c r="I5" s="3"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
@@ -465,128 +465,136 @@
         <v>4</v>
       </c>
       <c r="C6" s="4"/>
-      <c r="D6" s="4">
+      <c r="D6" s="3">
         <v>0.69365732956012705</v>
       </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4">
+      <c r="E6" s="3"/>
+      <c r="F6" s="3">
         <v>0.387796793163461</v>
       </c>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3">
+        <v>0.61811502129722296</v>
+      </c>
+      <c r="I6" s="3"/>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
+      <c r="B7" s="3">
+        <v>5</v>
+      </c>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3">
+        <v>0.95053371261328801</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3">
+        <v>0.88011314419879605</v>
+      </c>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
     </row>
     <row r="14" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
@@ -594,42 +602,6 @@
     </row>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="D2:E2"/>
@@ -646,6 +618,42 @@
     <mergeCell ref="H10:I10"/>
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="F7:G7"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F12:G12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Function 2/evals.xlsx
+++ b/Function 2/evals.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prithvi\Desktop\Imperial Course\Capstone-Project\Function 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C30A23B-3490-468F-8CED-5FCA8D87D394}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E39A3120-7FDA-4843-8DFF-EEEBB2826DB2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -84,10 +84,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -377,38 +377,38 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4" t="s">
+      <c r="C2" s="3"/>
+      <c r="D2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4" t="s">
+      <c r="E2" s="3"/>
+      <c r="F2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4" t="s">
+      <c r="G2" s="3"/>
+      <c r="H2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="4"/>
+      <c r="I2" s="3"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B3" s="4">
+      <c r="B3" s="3">
         <v>1</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="3">
+      <c r="C3" s="3"/>
+      <c r="D3" s="4">
         <v>0.71402200000000005</v>
       </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3">
+      <c r="E3" s="4"/>
+      <c r="F3" s="4">
         <v>0.14477200000000001</v>
       </c>
-      <c r="G3" s="3"/>
+      <c r="G3" s="4"/>
       <c r="H3" s="5">
         <v>0.59747244630609897</v>
       </c>
@@ -417,66 +417,66 @@
       <c r="K3" s="1"/>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B4" s="4">
+      <c r="B4" s="3">
         <v>2</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="3">
+      <c r="C4" s="3"/>
+      <c r="D4" s="4">
         <v>0.74275198707938395</v>
       </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3">
+      <c r="E4" s="4"/>
+      <c r="F4" s="4">
         <v>0.88397478133732699</v>
       </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3">
+      <c r="G4" s="4"/>
+      <c r="H4" s="4">
         <v>0.37689874596557199</v>
       </c>
-      <c r="I4" s="3"/>
+      <c r="I4" s="4"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B5" s="4">
+      <c r="B5" s="3">
         <v>3</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="3">
+      <c r="C5" s="3"/>
+      <c r="D5" s="4">
         <v>0.67103219867563402</v>
       </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3">
+      <c r="E5" s="4"/>
+      <c r="F5" s="4">
         <v>1</v>
       </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3">
+      <c r="G5" s="4"/>
+      <c r="H5" s="4">
         <v>0.42858172097026598</v>
       </c>
-      <c r="I5" s="3"/>
+      <c r="I5" s="4"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B6" s="4">
+      <c r="B6" s="3">
         <v>4</v>
       </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="3">
+      <c r="C6" s="3"/>
+      <c r="D6" s="4">
         <v>0.69365732956012705</v>
       </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3">
+      <c r="E6" s="4"/>
+      <c r="F6" s="4">
         <v>0.387796793163461</v>
       </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3">
+      <c r="G6" s="4"/>
+      <c r="H6" s="4">
         <v>0.61811502129722296</v>
       </c>
-      <c r="I6" s="3"/>
+      <c r="I6" s="4"/>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
@@ -487,114 +487,114 @@
         <v>5</v>
       </c>
       <c r="C7" s="3"/>
-      <c r="D7" s="3">
+      <c r="D7" s="4">
         <v>0.95053371261328801</v>
       </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3">
+      <c r="E7" s="4"/>
+      <c r="F7" s="4">
         <v>0.88011314419879605</v>
       </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
     </row>
     <row r="14" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
@@ -602,6 +602,42 @@
     </row>
   </sheetData>
   <mergeCells count="52">
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="D2:E2"/>
@@ -618,42 +654,6 @@
     <mergeCell ref="H10:I10"/>
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="F7:G7"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F12:G12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Function 2/evals.xlsx
+++ b/Function 2/evals.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prithvi\Desktop\Imperial Course\Capstone-Project\Function 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E39A3120-7FDA-4843-8DFF-EEEBB2826DB2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D756B00-252F-4B33-B691-360860436BC7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -84,10 +84,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -377,38 +377,38 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3" t="s">
+      <c r="C2" s="4"/>
+      <c r="D2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3" t="s">
+      <c r="E2" s="4"/>
+      <c r="F2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3" t="s">
+      <c r="G2" s="4"/>
+      <c r="H2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="3"/>
+      <c r="I2" s="4"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B3" s="3">
+      <c r="B3" s="4">
         <v>1</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="4">
+      <c r="C3" s="4"/>
+      <c r="D3" s="3">
         <v>0.71402200000000005</v>
       </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4">
+      <c r="E3" s="3"/>
+      <c r="F3" s="3">
         <v>0.14477200000000001</v>
       </c>
-      <c r="G3" s="4"/>
+      <c r="G3" s="3"/>
       <c r="H3" s="5">
         <v>0.59747244630609897</v>
       </c>
@@ -417,184 +417,192 @@
       <c r="K3" s="1"/>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B4" s="3">
+      <c r="B4" s="4">
         <v>2</v>
       </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="4">
+      <c r="C4" s="4"/>
+      <c r="D4" s="3">
         <v>0.74275198707938395</v>
       </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4">
+      <c r="E4" s="3"/>
+      <c r="F4" s="3">
         <v>0.88397478133732699</v>
       </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4">
+      <c r="G4" s="3"/>
+      <c r="H4" s="3">
         <v>0.37689874596557199</v>
       </c>
-      <c r="I4" s="4"/>
+      <c r="I4" s="3"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B5" s="3">
+      <c r="B5" s="4">
         <v>3</v>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="4">
+      <c r="C5" s="4"/>
+      <c r="D5" s="3">
         <v>0.67103219867563402</v>
       </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4">
+      <c r="E5" s="3"/>
+      <c r="F5" s="3">
         <v>1</v>
       </c>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4">
+      <c r="G5" s="3"/>
+      <c r="H5" s="3">
         <v>0.42858172097026598</v>
       </c>
-      <c r="I5" s="4"/>
+      <c r="I5" s="3"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B6" s="3">
+      <c r="B6" s="4">
         <v>4</v>
       </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="4">
+      <c r="C6" s="4"/>
+      <c r="D6" s="3">
         <v>0.69365732956012705</v>
       </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4">
+      <c r="E6" s="3"/>
+      <c r="F6" s="3">
         <v>0.387796793163461</v>
       </c>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4">
+      <c r="G6" s="3"/>
+      <c r="H6" s="3">
         <v>0.61811502129722296</v>
       </c>
-      <c r="I6" s="4"/>
+      <c r="I6" s="3"/>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B7" s="3">
+      <c r="B7" s="4">
         <v>5</v>
       </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="4">
+      <c r="C7" s="4"/>
+      <c r="D7" s="3">
         <v>0.95053371261328801</v>
       </c>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4">
+      <c r="E7" s="3"/>
+      <c r="F7" s="3">
         <v>0.88011314419879605</v>
       </c>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3">
+        <v>-4.6219718386069997E-3</v>
+      </c>
+      <c r="I7" s="3"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
+      <c r="B8" s="3">
+        <v>6</v>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3">
+        <v>0.70712306263689295</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3">
+        <v>0.56908739341997805</v>
+      </c>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
     </row>
     <row r="14" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
@@ -602,42 +610,6 @@
     </row>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="D2:E2"/>
@@ -654,6 +626,42 @@
     <mergeCell ref="H10:I10"/>
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="F7:G7"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F12:G12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Function 2/evals.xlsx
+++ b/Function 2/evals.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prithvi\Desktop\Imperial Course\Capstone-Project\Function 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D756B00-252F-4B33-B691-360860436BC7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDC1B30E-3300-4747-A6FC-26C070B0EE8B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -84,10 +84,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -374,41 +374,41 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:M14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B2" s="4" t="s">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4" t="s">
+      <c r="C2" s="3"/>
+      <c r="D2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4" t="s">
+      <c r="E2" s="3"/>
+      <c r="F2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4" t="s">
+      <c r="G2" s="3"/>
+      <c r="H2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="4"/>
+      <c r="I2" s="3"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B3" s="4">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B3" s="3">
         <v>1</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="3">
+      <c r="C3" s="3"/>
+      <c r="D3" s="4">
         <v>0.71402200000000005</v>
       </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3">
+      <c r="E3" s="4"/>
+      <c r="F3" s="4">
         <v>0.14477200000000001</v>
       </c>
-      <c r="G3" s="3"/>
+      <c r="G3" s="4"/>
       <c r="H3" s="5">
         <v>0.59747244630609897</v>
       </c>
@@ -416,193 +416,201 @@
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B4" s="4">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B4" s="3">
         <v>2</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="3">
+      <c r="C4" s="3"/>
+      <c r="D4" s="4">
         <v>0.74275198707938395</v>
       </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3">
+      <c r="E4" s="4"/>
+      <c r="F4" s="4">
         <v>0.88397478133732699</v>
       </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3">
+      <c r="G4" s="4"/>
+      <c r="H4" s="4">
         <v>0.37689874596557199</v>
       </c>
-      <c r="I4" s="3"/>
+      <c r="I4" s="4"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B5" s="4">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B5" s="3">
         <v>3</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="3">
+      <c r="C5" s="3"/>
+      <c r="D5" s="4">
         <v>0.67103219867563402</v>
       </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3">
+      <c r="E5" s="4"/>
+      <c r="F5" s="4">
         <v>1</v>
       </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3">
+      <c r="G5" s="4"/>
+      <c r="H5" s="4">
         <v>0.42858172097026598</v>
       </c>
-      <c r="I5" s="3"/>
+      <c r="I5" s="4"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B6" s="4">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B6" s="3">
         <v>4</v>
       </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="3">
+      <c r="C6" s="3"/>
+      <c r="D6" s="4">
         <v>0.69365732956012705</v>
       </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3">
+      <c r="E6" s="4"/>
+      <c r="F6" s="4">
         <v>0.387796793163461</v>
       </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3">
+      <c r="G6" s="4"/>
+      <c r="H6" s="4">
         <v>0.61811502129722296</v>
       </c>
-      <c r="I6" s="3"/>
+      <c r="I6" s="4"/>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B7" s="4">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B7" s="3">
         <v>5</v>
       </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="3">
+      <c r="C7" s="3"/>
+      <c r="D7" s="4">
         <v>0.95053371261328801</v>
       </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3">
+      <c r="E7" s="4"/>
+      <c r="F7" s="4">
         <v>0.88011314419879605</v>
       </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3">
+      <c r="G7" s="4"/>
+      <c r="H7" s="4">
         <v>-4.6219718386069997E-3</v>
       </c>
-      <c r="I7" s="3"/>
+      <c r="I7" s="4"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B8" s="3">
         <v>6</v>
       </c>
       <c r="C8" s="3"/>
-      <c r="D8" s="3">
+      <c r="D8" s="4">
         <v>0.70712306263689295</v>
       </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3">
+      <c r="E8" s="4"/>
+      <c r="F8" s="4">
         <v>0.56908739341997805</v>
       </c>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4">
+        <v>0.52965710858852499</v>
+      </c>
+      <c r="I8" s="4"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B9" s="3"/>
+    <row r="9" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B9" s="3">
+        <v>7</v>
+      </c>
       <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
+      <c r="D9" s="4">
+        <v>0.69469663231443302</v>
+      </c>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
+    <row r="14" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
@@ -610,6 +618,42 @@
     </row>
   </sheetData>
   <mergeCells count="52">
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="D2:E2"/>
@@ -626,42 +670,6 @@
     <mergeCell ref="H10:I10"/>
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="F7:G7"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F12:G12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Function 2/evals.xlsx
+++ b/Function 2/evals.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prithvi\Desktop\Imperial Course\Capstone-Project\Function 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDC1B30E-3300-4747-A6FC-26C070B0EE8B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2921DA2-E9F9-49C6-8AB8-C71AA1F3837A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -84,10 +84,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -374,41 +374,41 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:M14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B2" s="3" t="s">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3" t="s">
+      <c r="C2" s="4"/>
+      <c r="D2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3" t="s">
+      <c r="E2" s="4"/>
+      <c r="F2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3" t="s">
+      <c r="G2" s="4"/>
+      <c r="H2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="3"/>
+      <c r="I2" s="4"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B3" s="3">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B3" s="4">
         <v>1</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="4">
+      <c r="C3" s="4"/>
+      <c r="D3" s="3">
         <v>0.71402200000000005</v>
       </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4">
+      <c r="E3" s="3"/>
+      <c r="F3" s="3">
         <v>0.14477200000000001</v>
       </c>
-      <c r="G3" s="4"/>
+      <c r="G3" s="3"/>
       <c r="H3" s="5">
         <v>0.59747244630609897</v>
       </c>
@@ -416,201 +416,209 @@
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B4" s="3">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B4" s="4">
         <v>2</v>
       </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="4">
+      <c r="C4" s="4"/>
+      <c r="D4" s="3">
         <v>0.74275198707938395</v>
       </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4">
+      <c r="E4" s="3"/>
+      <c r="F4" s="3">
         <v>0.88397478133732699</v>
       </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4">
+      <c r="G4" s="3"/>
+      <c r="H4" s="3">
         <v>0.37689874596557199</v>
       </c>
-      <c r="I4" s="4"/>
+      <c r="I4" s="3"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B5" s="3">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B5" s="4">
         <v>3</v>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="4">
+      <c r="C5" s="4"/>
+      <c r="D5" s="3">
         <v>0.67103219867563402</v>
       </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4">
+      <c r="E5" s="3"/>
+      <c r="F5" s="3">
         <v>1</v>
       </c>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4">
+      <c r="G5" s="3"/>
+      <c r="H5" s="3">
         <v>0.42858172097026598</v>
       </c>
-      <c r="I5" s="4"/>
+      <c r="I5" s="3"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B6" s="3">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B6" s="4">
         <v>4</v>
       </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="4">
+      <c r="C6" s="4"/>
+      <c r="D6" s="3">
         <v>0.69365732956012705</v>
       </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4">
+      <c r="E6" s="3"/>
+      <c r="F6" s="3">
         <v>0.387796793163461</v>
       </c>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4">
+      <c r="G6" s="3"/>
+      <c r="H6" s="3">
         <v>0.61811502129722296</v>
       </c>
-      <c r="I6" s="4"/>
+      <c r="I6" s="3"/>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B7" s="3">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B7" s="4">
         <v>5</v>
       </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="4">
+      <c r="C7" s="4"/>
+      <c r="D7" s="3">
         <v>0.95053371261328801</v>
       </c>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4">
+      <c r="E7" s="3"/>
+      <c r="F7" s="3">
         <v>0.88011314419879605</v>
       </c>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4">
+      <c r="G7" s="3"/>
+      <c r="H7" s="3">
         <v>-4.6219718386069997E-3</v>
       </c>
-      <c r="I7" s="4"/>
+      <c r="I7" s="3"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B8" s="3">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B8" s="4">
         <v>6</v>
       </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="4">
+      <c r="C8" s="4"/>
+      <c r="D8" s="3">
         <v>0.70712306263689295</v>
       </c>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4">
+      <c r="E8" s="3"/>
+      <c r="F8" s="3">
         <v>0.56908739341997805</v>
       </c>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4">
+      <c r="G8" s="3"/>
+      <c r="H8" s="3">
         <v>0.52965710858852499</v>
       </c>
-      <c r="I8" s="4"/>
+      <c r="I8" s="3"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B9" s="3">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B9" s="4">
         <v>7</v>
       </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="4">
+      <c r="C9" s="4"/>
+      <c r="D9" s="3">
         <v>0.69469663231443302</v>
       </c>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4">
+      <c r="E9" s="3"/>
+      <c r="F9" s="3">
         <v>0</v>
       </c>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3">
+        <v>0.62494672793609396</v>
+      </c>
+      <c r="I9" s="3"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B10" s="4"/>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B10" s="4">
+        <v>8</v>
+      </c>
       <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
+      <c r="D10" s="3">
+        <v>0.69534207075710197</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3">
+        <v>2.12062580520909E-2</v>
+      </c>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
+    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
@@ -618,42 +626,6 @@
     </row>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="D2:E2"/>
@@ -670,6 +642,42 @@
     <mergeCell ref="H10:I10"/>
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="F7:G7"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F12:G12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Function 2/evals.xlsx
+++ b/Function 2/evals.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prithvi\Desktop\Imperial Course\Capstone-Project\Function 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2921DA2-E9F9-49C6-8AB8-C71AA1F3837A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21A2337F-5765-44FB-99B2-CC77A319B01E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -84,10 +84,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -374,41 +374,41 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:M14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B2" s="4" t="s">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4" t="s">
+      <c r="C2" s="3"/>
+      <c r="D2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4" t="s">
+      <c r="E2" s="3"/>
+      <c r="F2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4" t="s">
+      <c r="G2" s="3"/>
+      <c r="H2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="4"/>
+      <c r="I2" s="3"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B3" s="4">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B3" s="3">
         <v>1</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="3">
+      <c r="C3" s="3"/>
+      <c r="D3" s="4">
         <v>0.71402200000000005</v>
       </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3">
+      <c r="E3" s="4"/>
+      <c r="F3" s="4">
         <v>0.14477200000000001</v>
       </c>
-      <c r="G3" s="3"/>
+      <c r="G3" s="4"/>
       <c r="H3" s="5">
         <v>0.59747244630609897</v>
       </c>
@@ -416,209 +416,223 @@
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B4" s="4">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B4" s="3">
         <v>2</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="3">
+      <c r="C4" s="3"/>
+      <c r="D4" s="4">
         <v>0.74275198707938395</v>
       </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3">
+      <c r="E4" s="4"/>
+      <c r="F4" s="4">
         <v>0.88397478133732699</v>
       </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3">
+      <c r="G4" s="4"/>
+      <c r="H4" s="4">
         <v>0.37689874596557199</v>
       </c>
-      <c r="I4" s="3"/>
+      <c r="I4" s="4"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B5" s="4">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B5" s="3">
         <v>3</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="3">
+      <c r="C5" s="3"/>
+      <c r="D5" s="4">
         <v>0.67103219867563402</v>
       </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3">
+      <c r="E5" s="4"/>
+      <c r="F5" s="4">
         <v>1</v>
       </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3">
+      <c r="G5" s="4"/>
+      <c r="H5" s="4">
         <v>0.42858172097026598</v>
       </c>
-      <c r="I5" s="3"/>
+      <c r="I5" s="4"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B6" s="4">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B6" s="3">
         <v>4</v>
       </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="3">
+      <c r="C6" s="3"/>
+      <c r="D6" s="4">
         <v>0.69365732956012705</v>
       </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3">
+      <c r="E6" s="4"/>
+      <c r="F6" s="4">
         <v>0.387796793163461</v>
       </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3">
+      <c r="G6" s="4"/>
+      <c r="H6" s="4">
         <v>0.61811502129722296</v>
       </c>
-      <c r="I6" s="3"/>
+      <c r="I6" s="4"/>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B7" s="4">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B7" s="3">
         <v>5</v>
       </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="3">
+      <c r="C7" s="3"/>
+      <c r="D7" s="4">
         <v>0.95053371261328801</v>
       </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3">
+      <c r="E7" s="4"/>
+      <c r="F7" s="4">
         <v>0.88011314419879605</v>
       </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3">
+      <c r="G7" s="4"/>
+      <c r="H7" s="4">
         <v>-4.6219718386069997E-3</v>
       </c>
-      <c r="I7" s="3"/>
+      <c r="I7" s="4"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B8" s="4">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B8" s="3">
         <v>6</v>
       </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="3">
+      <c r="C8" s="3"/>
+      <c r="D8" s="4">
         <v>0.70712306263689295</v>
       </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3">
+      <c r="E8" s="4"/>
+      <c r="F8" s="4">
         <v>0.56908739341997805</v>
       </c>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3">
+      <c r="G8" s="4"/>
+      <c r="H8" s="4">
         <v>0.52965710858852499</v>
       </c>
-      <c r="I8" s="3"/>
+      <c r="I8" s="4"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B9" s="4">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B9" s="3">
         <v>7</v>
       </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="3">
+      <c r="C9" s="3"/>
+      <c r="D9" s="4">
         <v>0.69469663231443302</v>
       </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3">
+      <c r="E9" s="4"/>
+      <c r="F9" s="4">
         <v>0</v>
       </c>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3">
+      <c r="G9" s="4"/>
+      <c r="H9" s="4">
         <v>0.62494672793609396</v>
       </c>
-      <c r="I9" s="3"/>
+      <c r="I9" s="4"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B10" s="4">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B10" s="3">
         <v>8</v>
       </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="3">
+      <c r="C10" s="3"/>
+      <c r="D10" s="4">
         <v>0.69534207075710197</v>
       </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3">
+      <c r="E10" s="4"/>
+      <c r="F10" s="4">
         <v>2.12062580520909E-2</v>
       </c>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4">
+        <v>0.80847431394096902</v>
+      </c>
+      <c r="I10" s="4"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B11" s="3"/>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B11" s="3">
+        <v>9</v>
+      </c>
       <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
+      <c r="D11" s="4">
+        <v>0.69492788625802804</v>
+      </c>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B12" s="3"/>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B12" s="3">
+        <v>10</v>
+      </c>
       <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B13" s="3"/>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B13" s="3">
+        <v>11</v>
+      </c>
       <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B14" s="3"/>
+    <row r="14" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B14" s="3">
+        <v>12</v>
+      </c>
       <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
@@ -626,6 +640,42 @@
     </row>
   </sheetData>
   <mergeCells count="52">
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="D2:E2"/>
@@ -642,42 +692,6 @@
     <mergeCell ref="H10:I10"/>
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="F7:G7"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F12:G12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Function 2/evals.xlsx
+++ b/Function 2/evals.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prithvi\Desktop\Imperial Course\Capstone-Project\Function 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21A2337F-5765-44FB-99B2-CC77A319B01E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F29E80F5-169E-4E97-9620-229D64CCB42E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -84,10 +84,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -374,41 +374,41 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:M14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B2" s="3" t="s">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3" t="s">
+      <c r="C2" s="4"/>
+      <c r="D2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3" t="s">
+      <c r="E2" s="4"/>
+      <c r="F2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3" t="s">
+      <c r="G2" s="4"/>
+      <c r="H2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="3"/>
+      <c r="I2" s="4"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B3" s="3">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B3" s="4">
         <v>1</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="4">
-        <v>0.71402200000000005</v>
-      </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4">
-        <v>0.14477200000000001</v>
-      </c>
-      <c r="G3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="3">
+        <v>0.714022563</v>
+      </c>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3">
+        <v>0.14477253100000001</v>
+      </c>
+      <c r="G3" s="3"/>
       <c r="H3" s="5">
         <v>0.59747244630609897</v>
       </c>
@@ -416,223 +416,229 @@
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B4" s="3">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B4" s="4">
         <v>2</v>
       </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="4">
+      <c r="C4" s="4"/>
+      <c r="D4" s="3">
         <v>0.74275198707938395</v>
       </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4">
+      <c r="E4" s="3"/>
+      <c r="F4" s="3">
         <v>0.88397478133732699</v>
       </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4">
+      <c r="G4" s="3"/>
+      <c r="H4" s="3">
         <v>0.37689874596557199</v>
       </c>
-      <c r="I4" s="4"/>
+      <c r="I4" s="3"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B5" s="3">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B5" s="4">
         <v>3</v>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="4">
+      <c r="C5" s="4"/>
+      <c r="D5" s="3">
         <v>0.67103219867563402</v>
       </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4">
+      <c r="E5" s="3"/>
+      <c r="F5" s="3">
         <v>1</v>
       </c>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4">
+      <c r="G5" s="3"/>
+      <c r="H5" s="3">
         <v>0.42858172097026598</v>
       </c>
-      <c r="I5" s="4"/>
+      <c r="I5" s="3"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B6" s="3">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B6" s="4">
         <v>4</v>
       </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="4">
+      <c r="C6" s="4"/>
+      <c r="D6" s="3">
         <v>0.69365732956012705</v>
       </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4">
+      <c r="E6" s="3"/>
+      <c r="F6" s="3">
         <v>0.387796793163461</v>
       </c>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4">
+      <c r="G6" s="3"/>
+      <c r="H6" s="3">
         <v>0.61811502129722296</v>
       </c>
-      <c r="I6" s="4"/>
+      <c r="I6" s="3"/>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B7" s="3">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B7" s="4">
         <v>5</v>
       </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="4">
+      <c r="C7" s="4"/>
+      <c r="D7" s="3">
         <v>0.95053371261328801</v>
       </c>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4">
+      <c r="E7" s="3"/>
+      <c r="F7" s="3">
         <v>0.88011314419879605</v>
       </c>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4">
+      <c r="G7" s="3"/>
+      <c r="H7" s="3">
         <v>-4.6219718386069997E-3</v>
       </c>
-      <c r="I7" s="4"/>
+      <c r="I7" s="3"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B8" s="3">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B8" s="4">
         <v>6</v>
       </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="4">
+      <c r="C8" s="4"/>
+      <c r="D8" s="3">
         <v>0.70712306263689295</v>
       </c>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4">
+      <c r="E8" s="3"/>
+      <c r="F8" s="3">
         <v>0.56908739341997805</v>
       </c>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4">
+      <c r="G8" s="3"/>
+      <c r="H8" s="3">
         <v>0.52965710858852499</v>
       </c>
-      <c r="I8" s="4"/>
+      <c r="I8" s="3"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B9" s="3">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B9" s="4">
         <v>7</v>
       </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="4">
+      <c r="C9" s="4"/>
+      <c r="D9" s="3">
         <v>0.69469663231443302</v>
       </c>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4">
+      <c r="E9" s="3"/>
+      <c r="F9" s="3">
         <v>0</v>
       </c>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4">
+      <c r="G9" s="3"/>
+      <c r="H9" s="3">
         <v>0.62494672793609396</v>
       </c>
-      <c r="I9" s="4"/>
+      <c r="I9" s="3"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B10" s="3">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B10" s="4">
         <v>8</v>
       </c>
-      <c r="C10" s="3"/>
-      <c r="D10" s="4">
+      <c r="C10" s="4"/>
+      <c r="D10" s="3">
         <v>0.69534207075710197</v>
       </c>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4">
+      <c r="E10" s="3"/>
+      <c r="F10" s="3">
         <v>2.12062580520909E-2</v>
       </c>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4">
+      <c r="G10" s="3"/>
+      <c r="H10" s="3">
         <v>0.80847431394096902</v>
       </c>
-      <c r="I10" s="4"/>
+      <c r="I10" s="3"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B11" s="3">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B11" s="4">
         <v>9</v>
       </c>
-      <c r="C11" s="3"/>
-      <c r="D11" s="4">
+      <c r="C11" s="4"/>
+      <c r="D11" s="3">
         <v>0.69492788625802804</v>
       </c>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4">
+      <c r="E11" s="3"/>
+      <c r="F11" s="3">
         <v>0</v>
       </c>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3">
+        <v>0.46788977921349201</v>
+      </c>
+      <c r="I11" s="3"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B12" s="3">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B12" s="4">
         <v>10</v>
       </c>
-      <c r="C12" s="3"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="3">
+        <v>0.69721154046056499</v>
+      </c>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3">
+        <v>7.6625878251437907E-2</v>
+      </c>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B13" s="3">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B13" s="4">
         <v>11</v>
       </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B14" s="3">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B14" s="4">
         <v>12</v>
       </c>
-      <c r="C14" s="3"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
@@ -640,42 +646,6 @@
     </row>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="D2:E2"/>
@@ -692,6 +662,42 @@
     <mergeCell ref="H10:I10"/>
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="F7:G7"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F12:G12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Function 2/evals.xlsx
+++ b/Function 2/evals.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prithvi\Desktop\Imperial Course\Capstone-Project\Function 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F29E80F5-169E-4E97-9620-229D64CCB42E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25A7D19E-7F0C-4A1C-9E72-EE52D07F4E2B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -84,10 +84,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -377,38 +377,38 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4" t="s">
+      <c r="C2" s="3"/>
+      <c r="D2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4" t="s">
+      <c r="E2" s="3"/>
+      <c r="F2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4" t="s">
+      <c r="G2" s="3"/>
+      <c r="H2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="4"/>
+      <c r="I2" s="3"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B3" s="4">
+      <c r="B3" s="3">
         <v>1</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="3">
+      <c r="C3" s="3"/>
+      <c r="D3" s="4">
         <v>0.714022563</v>
       </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3">
+      <c r="E3" s="4"/>
+      <c r="F3" s="4">
         <v>0.14477253100000001</v>
       </c>
-      <c r="G3" s="3"/>
+      <c r="G3" s="4"/>
       <c r="H3" s="5">
         <v>0.59747244630609897</v>
       </c>
@@ -417,228 +417,234 @@
       <c r="K3" s="1"/>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B4" s="4">
+      <c r="B4" s="3">
         <v>2</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="3">
+      <c r="C4" s="3"/>
+      <c r="D4" s="4">
         <v>0.74275198707938395</v>
       </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3">
+      <c r="E4" s="4"/>
+      <c r="F4" s="4">
         <v>0.88397478133732699</v>
       </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3">
+      <c r="G4" s="4"/>
+      <c r="H4" s="4">
         <v>0.37689874596557199</v>
       </c>
-      <c r="I4" s="3"/>
+      <c r="I4" s="4"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B5" s="4">
+      <c r="B5" s="3">
         <v>3</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="3">
+      <c r="C5" s="3"/>
+      <c r="D5" s="4">
         <v>0.67103219867563402</v>
       </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3">
+      <c r="E5" s="4"/>
+      <c r="F5" s="4">
         <v>1</v>
       </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3">
+      <c r="G5" s="4"/>
+      <c r="H5" s="4">
         <v>0.42858172097026598</v>
       </c>
-      <c r="I5" s="3"/>
+      <c r="I5" s="4"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B6" s="4">
+      <c r="B6" s="3">
         <v>4</v>
       </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="3">
+      <c r="C6" s="3"/>
+      <c r="D6" s="4">
         <v>0.69365732956012705</v>
       </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3">
+      <c r="E6" s="4"/>
+      <c r="F6" s="4">
         <v>0.387796793163461</v>
       </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3">
+      <c r="G6" s="4"/>
+      <c r="H6" s="4">
         <v>0.61811502129722296</v>
       </c>
-      <c r="I6" s="3"/>
+      <c r="I6" s="4"/>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B7" s="4">
+      <c r="B7" s="3">
         <v>5</v>
       </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="3">
+      <c r="C7" s="3"/>
+      <c r="D7" s="4">
         <v>0.95053371261328801</v>
       </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3">
+      <c r="E7" s="4"/>
+      <c r="F7" s="4">
         <v>0.88011314419879605</v>
       </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3">
+      <c r="G7" s="4"/>
+      <c r="H7" s="4">
         <v>-4.6219718386069997E-3</v>
       </c>
-      <c r="I7" s="3"/>
+      <c r="I7" s="4"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B8" s="4">
+      <c r="B8" s="3">
         <v>6</v>
       </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="3">
+      <c r="C8" s="3"/>
+      <c r="D8" s="4">
         <v>0.70712306263689295</v>
       </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3">
+      <c r="E8" s="4"/>
+      <c r="F8" s="4">
         <v>0.56908739341997805</v>
       </c>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3">
+      <c r="G8" s="4"/>
+      <c r="H8" s="4">
         <v>0.52965710858852499</v>
       </c>
-      <c r="I8" s="3"/>
+      <c r="I8" s="4"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B9" s="4">
+      <c r="B9" s="3">
         <v>7</v>
       </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="3">
+      <c r="C9" s="3"/>
+      <c r="D9" s="4">
         <v>0.69469663231443302</v>
       </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3">
+      <c r="E9" s="4"/>
+      <c r="F9" s="4">
         <v>0</v>
       </c>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3">
+      <c r="G9" s="4"/>
+      <c r="H9" s="4">
         <v>0.62494672793609396</v>
       </c>
-      <c r="I9" s="3"/>
+      <c r="I9" s="4"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B10" s="4">
+      <c r="B10" s="3">
         <v>8</v>
       </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="3">
+      <c r="C10" s="3"/>
+      <c r="D10" s="4">
         <v>0.69534207075710197</v>
       </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3">
+      <c r="E10" s="4"/>
+      <c r="F10" s="4">
         <v>2.12062580520909E-2</v>
       </c>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3">
+      <c r="G10" s="4"/>
+      <c r="H10" s="4">
         <v>0.80847431394096902</v>
       </c>
-      <c r="I10" s="3"/>
+      <c r="I10" s="4"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B11" s="4">
+      <c r="B11" s="3">
         <v>9</v>
       </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="3">
+      <c r="C11" s="3"/>
+      <c r="D11" s="4">
         <v>0.69492788625802804</v>
       </c>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3">
+      <c r="E11" s="4"/>
+      <c r="F11" s="4">
         <v>0</v>
       </c>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3">
+      <c r="G11" s="4"/>
+      <c r="H11" s="4">
         <v>0.46788977921349201</v>
       </c>
-      <c r="I11" s="3"/>
+      <c r="I11" s="4"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B12" s="4">
+      <c r="B12" s="3">
         <v>10</v>
       </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="3">
+      <c r="C12" s="3"/>
+      <c r="D12" s="4">
         <v>0.69721154046056499</v>
       </c>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3">
+      <c r="E12" s="4"/>
+      <c r="F12" s="4">
         <v>7.6625878251437907E-2</v>
       </c>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4">
+        <v>0.7058792632209</v>
+      </c>
+      <c r="I12" s="4"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B13" s="4">
+      <c r="B13" s="3">
         <v>11</v>
       </c>
-      <c r="C13" s="4"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="4">
+        <v>0.69802586397619004</v>
+      </c>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4">
+        <v>4.40939648175298E-2</v>
+      </c>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
     </row>
     <row r="14" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B14" s="4">
+      <c r="B14" s="3">
         <v>12</v>
       </c>
-      <c r="C14" s="4"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
@@ -646,6 +652,42 @@
     </row>
   </sheetData>
   <mergeCells count="52">
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="D2:E2"/>
@@ -662,42 +704,6 @@
     <mergeCell ref="H10:I10"/>
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="F7:G7"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F12:G12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
